--- a/stories/arbres/TREE-LAN-019.xlsx
+++ b/stories/arbres/TREE-LAN-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Solal est au jardin avec papa. Des objets sont au sol. Papa dit : on compte des objets. Un, deux, trois. Solal touche. Il dit le nombre.</t>
+          <t>Solal est au jardin avec papa. Des objets sont au sol. On compte des objets. Un, deux, trois. Solal touche. Il dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1297,6 +1314,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Solal est au jardin avec papa. Des objets sont au sol.
+papa|On compte des objets.
+narrateur|Un, deux, trois. Solal touche. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1483,6 +1507,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac, le muret, ou l'allée.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1641,6 +1670,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1817,6 +1851,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, que fait Solal ?</t>
         </is>
       </c>
     </row>
@@ -1981,6 +2020,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Solal a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2167,6 +2211,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2325,6 +2374,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2511,6 +2565,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2669,6 +2728,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2831,6 +2895,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2989,6 +3058,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3151,6 +3225,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3309,6 +3388,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3471,6 +3555,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3629,6 +3718,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3815,6 +3909,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3973,6 +4072,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4135,6 +4239,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4293,6 +4402,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4455,6 +4569,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4613,6 +4732,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4775,6 +4899,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4933,6 +5062,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5119,6 +5253,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5277,6 +5416,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5439,6 +5583,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5597,6 +5746,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5759,6 +5913,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5917,6 +6076,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6079,6 +6243,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6237,6 +6406,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au muret, Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6413,6 +6587,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Au muret, que fait Solal ?</t>
         </is>
       </c>
     </row>
@@ -6577,6 +6756,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On compte des objets. On dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6763,6 +6947,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6921,6 +7110,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7107,6 +7301,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7265,6 +7464,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7427,6 +7631,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7585,6 +7794,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7747,6 +7961,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7905,6 +8124,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8067,6 +8291,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8225,6 +8454,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8411,6 +8645,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8569,6 +8808,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8731,6 +8975,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8889,6 +9138,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9051,6 +9305,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9209,6 +9468,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9371,6 +9635,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9529,6 +9798,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9715,6 +9989,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9873,6 +10152,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10035,6 +10319,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10193,6 +10482,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10355,6 +10649,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10513,6 +10812,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10675,6 +10979,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10833,6 +11142,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'allée, Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11009,6 +11323,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Dans l'allée, que fait Solal ?</t>
         </is>
       </c>
     </row>
@@ -11173,6 +11492,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Solal touche. Il compte. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11359,6 +11683,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11517,6 +11846,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11703,6 +12037,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11861,6 +12200,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12023,6 +12367,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12181,6 +12530,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12343,6 +12697,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12501,6 +12860,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12663,6 +13027,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12821,6 +13190,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13007,6 +13381,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13165,6 +13544,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13327,6 +13711,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13485,6 +13874,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13647,6 +14041,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13805,6 +14204,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13967,6 +14371,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14125,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14311,6 +14725,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14469,6 +14888,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à trois, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14631,6 +15055,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14789,6 +15218,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à cinq, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14951,6 +15385,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15109,6 +15548,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Solal s'arrête à dix, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15271,6 +15715,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15289,7 +15738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15306,6 +15755,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-019.xlsx
+++ b/stories/arbres/TREE-LAN-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Un, deux, trois. Solal touche. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1518,7 @@
           <t>narrateur|On peut prendre le bac, le muret, ou l'allée.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Au bac, Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1858,6 +1866,7 @@
           <t>narrateur|Au bac, que fait Solal ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2025,6 +2034,7 @@
           <t>narrateur|Solal a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2216,6 +2226,7 @@
           <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2379,6 +2390,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2570,6 +2582,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2733,6 +2746,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2900,6 +2914,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3063,6 +3078,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3230,6 +3246,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3393,6 +3410,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les galets, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3560,6 +3578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3723,6 +3742,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3914,6 +3934,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4077,6 +4098,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4244,6 +4266,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4407,6 +4430,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4574,6 +4598,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4737,6 +4762,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les feuilles, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4904,6 +4930,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5067,6 +5094,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5258,6 +5286,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5421,6 +5450,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5588,6 +5618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5751,6 +5782,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5918,6 +5950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6081,6 +6114,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les pommes, à le bac. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6248,6 +6282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6411,6 +6446,7 @@
           <t>narrateur|Au muret, Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6594,6 +6630,7 @@
           <t>narrateur|Au muret, que fait Solal ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6761,6 +6798,7 @@
           <t>narrateur|Oui. On compte des objets. On dit le nombre.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6952,6 +6990,7 @@
           <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7115,6 +7154,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7306,6 +7346,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7469,6 +7510,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7636,6 +7678,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7799,6 +7842,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7966,6 +8010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8129,6 +8174,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les galets, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8296,6 +8342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8459,6 +8506,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8650,6 +8698,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8813,6 +8862,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8980,6 +9030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9143,6 +9194,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9310,6 +9362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9473,6 +9526,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les feuilles, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9640,6 +9694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9803,6 +9858,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9994,6 +10050,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10157,6 +10214,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10324,6 +10382,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10487,6 +10546,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10654,6 +10714,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10817,6 +10878,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les pommes, à le muret. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10984,6 +11046,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11147,6 +11210,7 @@
           <t>narrateur|Dans l'allée, Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11330,6 +11394,7 @@
           <t>narrateur|Dans l'allée, que fait Solal ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11497,6 +11562,7 @@
           <t>narrateur|Solal touche. Il compte. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11688,6 +11754,7 @@
           <t>narrateur|On peut prendre les galets, les feuilles, ou les pommes.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11851,6 +11918,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12042,6 +12110,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12205,6 +12274,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12372,6 +12442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12535,6 +12606,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12702,6 +12774,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12865,6 +12938,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les galets, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13032,6 +13106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13195,6 +13270,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13386,6 +13462,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13549,6 +13626,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13716,6 +13794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13879,6 +13958,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14046,6 +14126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14209,6 +14290,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les feuilles, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14376,6 +14458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14539,6 +14622,7 @@
           <t>narrateur|Solal compte des objets. Il dit le nombre.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14730,6 +14814,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14893,6 +14978,7 @@
           <t>narrateur|Solal s'arrête à trois, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15060,6 +15146,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15223,6 +15310,7 @@
           <t>narrateur|Solal s'arrête à cinq, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15390,6 +15478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15553,6 +15642,7 @@
           <t>narrateur|Solal s'arrête à dix, avec les pommes, à l'allée. Il a compté des objets. Il a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15720,6 +15810,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15738,7 +15829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +15853,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15963,6 +16068,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
